--- a/Chap/Database/Presentations/Design/TableDesignTemplate.xlsx
+++ b/Chap/Database/Presentations/Design/TableDesignTemplate.xlsx
@@ -3,15 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38003075-6153-4170-A48F-8970F6824C51}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432F156C-52CC-4373-8B40-181A3936C516}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="5" r:id="rId1"/>
     <sheet name="Weapon" sheetId="7" r:id="rId2"/>
-    <sheet name="Character" sheetId="8" r:id="rId3"/>
-    <sheet name="WeaponV2" sheetId="9" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -206,7 +204,7 @@
     <author>Forfatter</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{804C5F74-8EDF-4D51-953B-0EB52CE30892}">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{E88869A6-BEDC-489A-A32F-46E08172C98C}">
       <text>
         <r>
           <rPr>
@@ -269,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{E1E61684-8A9C-47E2-BACA-AF32DB6C091D}">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{353BEE6A-8F82-490E-8E32-12764C7EE58C}">
       <text>
         <r>
           <rPr>
@@ -312,363 +310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{99C92FAC-58DB-4C91-B563-8D1BBD6F13F8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Forfatter:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Here you can add descriptions of </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>business rules</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> and </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>constraints</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> on the data, that cannot be expressed directly in the model itself.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Forfatter</author>
-  </authors>
-  <commentList>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{5CEA8026-0A15-4FD9-B7B2-6B460AAF1970}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Forfatter:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Here you define various </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>properties</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> for each column,
-i.e. this is </t>
-        </r>
-        <r>
-          <rPr>
-            <u/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>not</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> the actual data itself.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{D1B032F3-D921-4037-B747-3E6A3A88BAF1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Forfatter:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Here you can provide examples of </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>actual data</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> to be stored in the table.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{300D66E6-6EA5-4C4B-B71E-76563E40D1C2}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Forfatter:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Here you can add descriptions of </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>business rules</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> and </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>constraints</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> on the data, that cannot be expressed directly in the model itself.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Forfatter</author>
-  </authors>
-  <commentList>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{D4122A71-8A01-4A5D-A824-34D888143C89}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Forfatter:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Here you define various </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>properties</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> for each column,
-i.e. this is </t>
-        </r>
-        <r>
-          <rPr>
-            <u/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>not</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> the actual data itself.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{75DB196A-50EE-4A7C-99CC-B11E62C8FE3C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Forfatter:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Here you can provide examples of </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>actual data</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> to be stored in the table.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{4BD3BA0B-13A9-46FA-82F8-4B0B296B8412}">
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{F1D70CED-CE40-42F9-8F17-B024F4335E8C}">
       <text>
         <r>
           <rPr>
@@ -735,7 +377,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="43">
   <si>
     <t>Data Type</t>
   </si>
@@ -824,94 +466,46 @@
     <t>ZipCode between 1000 and 9999</t>
   </si>
   <si>
+    <t>Weapon</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
+    <t>Oathbringer</t>
+  </si>
+  <si>
+    <t>Avenger</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
     <t>Rarity</t>
   </si>
   <si>
-    <t>Og så videre…</t>
-  </si>
-  <si>
     <t>ItemLevel</t>
   </si>
   <si>
-    <t>Simple Sword</t>
-  </si>
-  <si>
-    <t>Sword</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>…</t>
-  </si>
-  <si>
-    <t>Beginner Gun</t>
-  </si>
-  <si>
-    <t>Gun</t>
-  </si>
-  <si>
-    <t>Master Sword</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Character</t>
-  </si>
-  <si>
-    <t>Race</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>HealthPoints</t>
-  </si>
-  <si>
-    <t>Peter</t>
-  </si>
-  <si>
-    <t>Human</t>
-  </si>
-  <si>
-    <t>Wizard</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
-    <t>Elf</t>
-  </si>
-  <si>
-    <t>Hunter</t>
-  </si>
-  <si>
-    <t>Eric</t>
-  </si>
-  <si>
-    <t>Dora</t>
-  </si>
-  <si>
-    <t>Warrior</t>
-  </si>
-  <si>
-    <t>WeaponInLeftHand</t>
-  </si>
-  <si>
-    <t>WeaponInRightHand</t>
-  </si>
-  <si>
-    <t>Weapon (V2)</t>
-  </si>
-  <si>
-    <t>WeaponModelName</t>
-  </si>
-  <si>
-    <t>Weapon / WeaponModel</t>
+    <t>MinDmg</t>
+  </si>
+  <si>
+    <t>MaxDmg</t>
+  </si>
+  <si>
+    <t>JewelSockets</t>
+  </si>
+  <si>
+    <t>IsTwoHanded</t>
+  </si>
+  <si>
+    <t>ItemLevel &gt; 0</t>
+  </si>
+  <si>
+    <t>Type er "Gun", "Sword", "Mace"</t>
+  </si>
+  <si>
+    <t>Rarity er "Common", "Rare", "Epic"</t>
   </si>
 </sst>
 </file>
@@ -1327,12 +921,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF32630-8A56-48A6-9D9E-96AF8F5C446B}">
   <dimension ref="B3:J24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="10" width="20.7109375" customWidth="1"/>
+    <col min="2" max="10" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
@@ -1344,12 +938,12 @@
       <c r="F3" s="1"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="6" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
         <v>2</v>
       </c>
@@ -1372,7 +966,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>9</v>
       </c>
@@ -1393,7 +987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="8" t="s">
         <v>10</v>
       </c>
@@ -1414,7 +1008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>0</v>
       </c>
@@ -1435,7 +1029,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>1</v>
       </c>
@@ -1456,7 +1050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
@@ -1479,7 +1073,7 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="6">
@@ -1500,7 +1094,7 @@
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="6">
@@ -1521,7 +1115,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="20" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1534,7 +1128,7 @@
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1542,7 +1136,7 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -1550,7 +1144,7 @@
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1558,7 +1152,7 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -1581,28 +1175,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC1C5A7-AE2B-4D09-A33F-6A8A5C58080E}">
-  <dimension ref="B3:H24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B354AF-8A51-4E27-959B-34C2A2307E4C}">
+  <dimension ref="B3:K24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="8" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" customWidth="1"/>
+    <col min="6" max="11" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2"/>
-    </row>
-    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E3" s="2"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="6" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
         <v>2</v>
       </c>
@@ -1611,19 +1210,28 @@
         <v>12</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>9</v>
       </c>
@@ -1640,9 +1248,20 @@
       <c r="G8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="8" t="s">
         <v>10</v>
       </c>
@@ -1654,14 +1273,25 @@
         <v>5</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>0</v>
       </c>
@@ -1673,14 +1303,25 @@
         <v>7</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="8"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>1</v>
       </c>
@@ -1697,531 +1338,148 @@
       <c r="G11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="14" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="11">
+      <c r="F14" s="6">
         <v>2</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G14" s="6">
+        <v>56</v>
+      </c>
+      <c r="H14" s="6">
+        <v>60</v>
+      </c>
+      <c r="I14" s="11">
+        <v>200</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="11">
+        <v>32</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="6">
         <v>3</v>
       </c>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G15" s="6">
+        <v>88</v>
+      </c>
+      <c r="H15" s="6">
+        <v>75</v>
+      </c>
+      <c r="I15" s="11">
+        <v>340</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="11">
-        <v>75</v>
-      </c>
-      <c r="H16" s="11"/>
-    </row>
-    <row r="20" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="20" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="12"/>
+      <c r="D20" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D21" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D21" s="12" t="s">
+        <v>41</v>
+      </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D22" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="E22" s="12"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="D24:I24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C61D0963-A0A8-43A1-9223-0F0D73945E8A}">
-  <dimension ref="B3:I24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="7" width="20.7109375" customWidth="1"/>
-    <col min="8" max="9" width="22.7109375" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="6" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="11">
-        <v>120</v>
-      </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="11">
-        <v>180</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="11">
-        <v>210</v>
-      </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="11">
-        <v>275</v>
-      </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-    </row>
-    <row r="20" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E636E1-8474-4830-8997-4F4665B01A82}">
-  <dimension ref="B3:E24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="6" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="6">
-        <v>2</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6">
-        <v>3</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="6">
-        <v>4</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="6">
-        <v>5</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="11"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="11"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="11"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="11"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E24" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>